--- a/simulations/AON_88/economics_AON_88.xlsx
+++ b/simulations/AON_88/economics_AON_88.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_88\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE792D0D-B1CE-4E44-9C02-E4307AC5E651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9C43A5-C7B3-4ED1-8A86-16DA28FCF459}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -3062,14 +3062,14 @@
         <v>94</v>
       </c>
       <c r="C23" s="17">
-        <v>37499.546953745201</v>
+        <v>37499.927281984797</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="17">
         <f>C23</f>
-        <v>37499.546953745201</v>
+        <v>37499.927281984797</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C24" s="44">
         <f>C22/C23</f>
-        <v>0.81252120771559888</v>
+        <v>0.81251296703933729</v>
       </c>
       <c r="E24" s="30" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="44">
         <f>F22/F23</f>
-        <v>1.3991363968370505</v>
+        <v>1.3991222066473266</v>
       </c>
     </row>
   </sheetData>

--- a/simulations/AON_88/economics_AON_88.xlsx
+++ b/simulations/AON_88/economics_AON_88.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_88\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9C43A5-C7B3-4ED1-8A86-16DA28FCF459}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E15EBF0-1337-4951-850C-20471BD2745D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="140">
   <si>
     <t>Cost factors</t>
   </si>
@@ -612,6 +612,21 @@
   </si>
   <si>
     <t>CEPCI 2017</t>
+  </si>
+  <si>
+    <t>Future fossil ammonia price</t>
+  </si>
+  <si>
+    <t>Future wind ammonia price</t>
+  </si>
+  <si>
+    <t>$ per ton</t>
+  </si>
+  <si>
+    <t>Current fossil ammonia price</t>
+  </si>
+  <si>
+    <t>Current wind ammonia price</t>
   </si>
 </sst>
 </file>
@@ -772,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -903,6 +918,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2467,7 +2483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:F19"/>
+  <dimension ref="B2:H25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="11"/>
@@ -2479,10 +2495,10 @@
     <col min="7" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>23</v>
       </c>
@@ -2499,7 +2515,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="49" t="s">
         <v>102</v>
       </c>
@@ -2508,7 +2524,7 @@
       <c r="E4" s="50"/>
       <c r="F4" s="50"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>99</v>
       </c>
@@ -2526,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>100</v>
       </c>
@@ -2544,8 +2560,12 @@
         <f>D6*E6</f>
         <v>25112.314322279995</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="11">
+        <f>F6/Summary!$C$23</f>
+        <v>0.66966301383587246</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="41" t="s">
         <v>103</v>
       </c>
@@ -2557,14 +2577,18 @@
         <v>34.486883999999996</v>
       </c>
       <c r="E7" s="42">
-        <v>1366.03</v>
+        <v>925.28408737229393</v>
       </c>
       <c r="F7" s="42">
         <f>D7*E7</f>
-        <v>47110.118150519993</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+        <v>31910.164988254161</v>
+      </c>
+      <c r="G7" s="11">
+        <f>F7/Summary!$C$23</f>
+        <v>0.85093938311672424</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="49" t="s">
         <v>104</v>
       </c>
@@ -2573,7 +2597,7 @@
       <c r="E8" s="50"/>
       <c r="F8" s="50"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
@@ -2592,8 +2616,12 @@
         <f>D9*E9</f>
         <v>89.284886116963477</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="11">
+        <f>F9/Summary!$C$23</f>
+        <v>2.3809349134353256E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>133</v>
       </c>
@@ -2612,8 +2640,16 @@
         <f>D10*E10</f>
         <v>3692.2206968867845</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="11">
+        <f>F10/Summary!$C$23</f>
+        <v>9.845940951092326E-2</v>
+      </c>
+      <c r="H10" s="11">
+        <f>SUM(G9:G10)</f>
+        <v>0.10084034442435859</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>25</v>
       </c>
@@ -2631,8 +2667,12 @@
         <f>D11*E11</f>
         <v>212.99013024768001</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="11">
+        <f>F11/Summary!$C$23</f>
+        <v>5.6797478204711569E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
         <v>106</v>
       </c>
@@ -2646,7 +2686,7 @@
         <v>232.85448028425134</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="36" t="s">
         <v>107</v>
       </c>
@@ -2657,17 +2697,17 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19">
         <f>(F5+F7+F9+F10+F11)/1000000*8000</f>
-        <v>408.8369109101713</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+        <v>287.23728561204473</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
         <v>85</v>
       </c>
@@ -2676,7 +2716,7 @@
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>134</v>
       </c>
@@ -2684,31 +2724,79 @@
         <v>567.5</v>
       </c>
       <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>135</v>
+      </c>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="23">
         <v>603.1</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="E17" s="56">
+        <f>E22*(100-ABS(G17))/100</f>
+        <v>650.66170868347331</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="11">
+        <v>-10.644257703081239</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="21">
         <v>607.5</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="E18" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
         <v>91</v>
       </c>
       <c r="C19" s="21">
         <v>816</v>
+      </c>
+      <c r="E19" s="56">
+        <f>0.925284087372294*1000</f>
+        <v>925.28408737229393</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E21" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E22" s="11">
+        <v>728.17</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E25" s="11">
+        <v>1366.03</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3022,7 +3110,7 @@
       </c>
       <c r="F20" s="17">
         <f>OPEX!F13</f>
-        <v>408.8369109101713</v>
+        <v>287.23728561204473</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -3038,7 +3126,7 @@
       </c>
       <c r="F21" s="17">
         <f>(F18+F19+F20)</f>
-        <v>419.73584806307883</v>
+        <v>298.13622276495227</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
@@ -3054,7 +3142,7 @@
       </c>
       <c r="F22" s="17">
         <f>(F21)*1000000/8000</f>
-        <v>52466.981007884853</v>
+        <v>37267.027845619028</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
@@ -3085,7 +3173,7 @@
       </c>
       <c r="F24" s="44">
         <f>F22/F23</f>
-        <v>1.3991222066473266</v>
+        <v>0.99378933632018918</v>
       </c>
     </row>
   </sheetData>
